--- a/results/all_results_tcn.xlsx
+++ b/results/all_results_tcn.xlsx
@@ -26,12 +26,24 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0000FF00"/>
+        <bgColor rgb="0000FF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000070C0"/>
+        <bgColor rgb="000070C0"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +58,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1743,140 +1757,140 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="1" t="inlineStr">
         <is>
           <t>2026-05-22_23-36-14</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="B10" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" s="1" t="n">
         <v>42</v>
       </c>
-      <c r="D10" t="b">
-        <v>1</v>
-      </c>
-      <c r="E10" t="b">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
+      <c r="D10" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F10" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>1</v>
-      </c>
-      <c r="I10" t="n">
+      <c r="G10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="1" t="n">
         <v>64</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J10" s="1" t="n">
         <v>0.2438031602295144</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K10" s="1" t="n">
         <v>32</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L10" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M10" s="1" t="n">
         <v>0.00248463381689824</v>
       </c>
-      <c r="N10" t="n">
+      <c r="N10" s="1" t="n">
         <v>45</v>
       </c>
-      <c r="O10" t="n">
+      <c r="O10" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="P10" t="n">
+      <c r="P10" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="Q10" s="1" t="n">
         <v>0.4692280519442701</v>
       </c>
-      <c r="R10" t="n">
+      <c r="R10" s="1" t="n">
         <v>0.33074162654379</v>
       </c>
-      <c r="S10" t="n">
+      <c r="S10" s="1" t="n">
         <v>0.8868191464277293</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T10" s="1" t="n">
         <v>0.8895469067451585</v>
       </c>
-      <c r="U10" t="n">
+      <c r="U10" s="1" t="n">
         <v>0.8868191464277293</v>
       </c>
-      <c r="V10" t="n">
+      <c r="V10" s="1" t="n">
         <v>0.8868067807082115</v>
       </c>
-      <c r="W10" t="n">
+      <c r="W10" s="1" t="n">
         <v>0.9786091279111153</v>
       </c>
-      <c r="X10" t="n">
+      <c r="X10" s="1" t="n">
         <v>0.4692280519442701</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="Y10" s="1" t="n">
         <v>0.8909081386823086</v>
       </c>
-      <c r="Z10" t="n">
+      <c r="Z10" s="1" t="n">
         <v>0.8951653700752311</v>
       </c>
-      <c r="AA10" t="n">
+      <c r="AA10" s="1" t="n">
         <v>0.8909081386823086</v>
       </c>
-      <c r="AB10" t="n">
+      <c r="AB10" s="1" t="n">
         <v>0.8847231501252966</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AC10" s="1" t="n">
         <v>0.9715780125261124</v>
       </c>
-      <c r="AD10" t="n">
+      <c r="AD10" s="1" t="n">
         <v>0.2057901083028276</v>
       </c>
-      <c r="AE10" t="n">
+      <c r="AE10" s="1" t="n">
         <v>0.9424950246150623</v>
       </c>
-      <c r="AF10" t="n">
+      <c r="AF10" s="1" t="n">
         <v>0.9420985691162979</v>
       </c>
-      <c r="AG10" t="n">
+      <c r="AG10" s="1" t="n">
         <v>0.9424950246150623</v>
       </c>
-      <c r="AH10" t="n">
+      <c r="AH10" s="1" t="n">
         <v>0.9413223604999386</v>
       </c>
-      <c r="AI10" t="n">
+      <c r="AI10" s="1" t="n">
         <v>0.9922196362764649</v>
       </c>
-      <c r="AJ10" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK10" t="n">
+      <c r="AJ10" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="AK10" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="AL10" t="n">
+      <c r="AL10" s="1" t="n">
         <v>78.23285095400206</v>
       </c>
-      <c r="AM10" t="b">
-        <v>1</v>
-      </c>
-      <c r="AN10" t="inlineStr">
+      <c r="AM10" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN10" s="1" t="inlineStr">
         <is>
           <t>NVIDIA GeForce RTX 5060</t>
         </is>
       </c>
-      <c r="AO10" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP10" t="n">
+      <c r="AO10" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP10" s="1" t="n">
         <v>92000</v>
       </c>
-      <c r="AQ10" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR10" t="b">
+      <c r="AQ10" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="AR10" s="1" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4365,140 +4379,140 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>2026-05-23_01-11-07</t>
         </is>
       </c>
-      <c r="B29" t="n">
+      <c r="B29" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="C29" t="n">
+      <c r="C29" s="2" t="n">
         <v>42</v>
       </c>
-      <c r="D29" t="b">
-        <v>1</v>
-      </c>
-      <c r="E29" t="b">
-        <v>0</v>
-      </c>
-      <c r="F29" t="n">
+      <c r="D29" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E29" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F29" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="G29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" t="n">
-        <v>1</v>
-      </c>
-      <c r="I29" t="n">
+      <c r="G29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="J29" t="n">
+      <c r="J29" s="2" t="n">
         <v>0.1398276356443244</v>
       </c>
-      <c r="K29" t="n">
+      <c r="K29" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="L29" t="n">
+      <c r="L29" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="M29" t="n">
+      <c r="M29" s="2" t="n">
         <v>0.0008679572756499553</v>
       </c>
-      <c r="N29" t="n">
+      <c r="N29" s="2" t="n">
         <v>47</v>
       </c>
-      <c r="O29" t="n">
+      <c r="O29" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="P29" t="n">
+      <c r="P29" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="Q29" s="2" t="n">
         <v>0.4468604328327964</v>
       </c>
-      <c r="R29" t="n">
+      <c r="R29" s="2" t="n">
         <v>0.3142144190361623</v>
       </c>
-      <c r="S29" t="n">
+      <c r="S29" s="2" t="n">
         <v>0.8959790700546828</v>
       </c>
-      <c r="T29" t="n">
+      <c r="T29" s="2" t="n">
         <v>0.900980759799187</v>
       </c>
-      <c r="U29" t="n">
+      <c r="U29" s="2" t="n">
         <v>0.8959790700546828</v>
       </c>
-      <c r="V29" t="n">
+      <c r="V29" s="2" t="n">
         <v>0.8955904056853582</v>
       </c>
-      <c r="W29" t="n">
+      <c r="W29" s="2" t="n">
         <v>0.9808937791210707</v>
       </c>
-      <c r="X29" t="n">
+      <c r="X29" s="2" t="n">
         <v>0.4468604328327964</v>
       </c>
-      <c r="Y29" t="n">
+      <c r="Y29" s="2" t="n">
         <v>0.8949408191054782</v>
       </c>
-      <c r="Z29" t="n">
+      <c r="Z29" s="2" t="n">
         <v>0.8980189066981664</v>
       </c>
-      <c r="AA29" t="n">
+      <c r="AA29" s="2" t="n">
         <v>0.8949408191054782</v>
       </c>
-      <c r="AB29" t="n">
+      <c r="AB29" s="2" t="n">
         <v>0.8881435281136164</v>
       </c>
-      <c r="AC29" t="n">
+      <c r="AC29" s="2" t="n">
         <v>0.9719201064562083</v>
       </c>
-      <c r="AD29" t="n">
+      <c r="AD29" s="2" t="n">
         <v>0.1934452463814637</v>
       </c>
-      <c r="AE29" t="n">
+      <c r="AE29" s="2" t="n">
         <v>0.9400858908557662</v>
       </c>
-      <c r="AF29" t="n">
+      <c r="AF29" s="2" t="n">
         <v>0.9403057238519894</v>
       </c>
-      <c r="AG29" t="n">
+      <c r="AG29" s="2" t="n">
         <v>0.9400858908557662</v>
       </c>
-      <c r="AH29" t="n">
+      <c r="AH29" s="2" t="n">
         <v>0.9386899356682086</v>
       </c>
-      <c r="AI29" t="n">
+      <c r="AI29" s="2" t="n">
         <v>0.9920884963655692</v>
       </c>
-      <c r="AJ29" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK29" t="n">
+      <c r="AJ29" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AK29" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="AL29" t="n">
+      <c r="AL29" s="2" t="n">
         <v>291.0554734269972</v>
       </c>
-      <c r="AM29" t="b">
-        <v>1</v>
-      </c>
-      <c r="AN29" t="inlineStr">
+      <c r="AM29" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN29" s="2" t="inlineStr">
         <is>
           <t>NVIDIA GeForce RTX 5060</t>
         </is>
       </c>
-      <c r="AO29" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP29" t="n">
+      <c r="AO29" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP29" s="2" t="n">
         <v>92000</v>
       </c>
-      <c r="AQ29" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR29" t="b">
+      <c r="AQ29" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AR29" s="2" t="b">
         <v>0</v>
       </c>
     </row>

--- a/results/all_results_tcn.xlsx
+++ b/results/all_results_tcn.xlsx
@@ -26,24 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0000FF00"/>
-        <bgColor rgb="0000FF00"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="000070C0"/>
-        <bgColor rgb="000070C0"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -58,10 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -427,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR31"/>
+  <dimension ref="A1:BA31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -651,6 +637,51 @@
           <t>cudnn_benchmark</t>
         </is>
       </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>train_macro_precision</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>train_macro_recall</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>train_macro_f1</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>val_macro_precision</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>val_macro_recall</t>
+        </is>
+      </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>val_macro_f1</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>test_macro_precision</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>test_macro_recall</t>
+        </is>
+      </c>
+      <c r="BA1" t="inlineStr">
+        <is>
+          <t>test_macro_f1</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -789,6 +820,33 @@
       <c r="AR2" t="b">
         <v>0</v>
       </c>
+      <c r="AS2" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>0.89</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -927,6 +985,33 @@
       <c r="AR3" t="b">
         <v>0</v>
       </c>
+      <c r="AS3" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>0.88</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1065,6 +1150,33 @@
       <c r="AR4" t="b">
         <v>0</v>
       </c>
+      <c r="AS4" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0.88</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1203,6 +1315,33 @@
       <c r="AR5" t="b">
         <v>0</v>
       </c>
+      <c r="AS5" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0.87</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1341,6 +1480,33 @@
       <c r="AR6" t="b">
         <v>0</v>
       </c>
+      <c r="AS6" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0.89</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1479,6 +1645,33 @@
       <c r="AR7" t="b">
         <v>0</v>
       </c>
+      <c r="AS7" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0.86</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1617,6 +1810,33 @@
       <c r="AR8" t="b">
         <v>0</v>
       </c>
+      <c r="AS8" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0.8100000000000001</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1755,143 +1975,197 @@
       <c r="AR9" t="b">
         <v>0</v>
       </c>
+      <c r="AS9" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0.84</v>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>2026-05-22_23-36-14</t>
         </is>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" t="n">
         <v>100</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" t="n">
         <v>42</v>
       </c>
-      <c r="D10" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="E10" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="F10" s="1" t="n">
+      <c r="D10" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" t="b">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
         <v>8</v>
       </c>
-      <c r="G10" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I10" s="1" t="n">
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n">
         <v>64</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" t="n">
         <v>0.2438031602295144</v>
       </c>
-      <c r="K10" s="1" t="n">
+      <c r="K10" t="n">
         <v>32</v>
       </c>
-      <c r="L10" s="1" t="n">
+      <c r="L10" t="n">
         <v>3</v>
       </c>
-      <c r="M10" s="1" t="n">
+      <c r="M10" t="n">
         <v>0.00248463381689824</v>
       </c>
-      <c r="N10" s="1" t="n">
+      <c r="N10" t="n">
         <v>45</v>
       </c>
-      <c r="O10" s="1" t="n">
+      <c r="O10" t="n">
         <v>5</v>
       </c>
-      <c r="P10" s="1" t="n">
+      <c r="P10" t="n">
         <v>8</v>
       </c>
-      <c r="Q10" s="1" t="n">
+      <c r="Q10" t="n">
         <v>0.4692280519442701</v>
       </c>
-      <c r="R10" s="1" t="n">
+      <c r="R10" t="n">
         <v>0.33074162654379</v>
       </c>
-      <c r="S10" s="1" t="n">
+      <c r="S10" t="n">
         <v>0.8868191464277293</v>
       </c>
-      <c r="T10" s="1" t="n">
+      <c r="T10" t="n">
         <v>0.8895469067451585</v>
       </c>
-      <c r="U10" s="1" t="n">
+      <c r="U10" t="n">
         <v>0.8868191464277293</v>
       </c>
-      <c r="V10" s="1" t="n">
+      <c r="V10" t="n">
         <v>0.8868067807082115</v>
       </c>
-      <c r="W10" s="1" t="n">
+      <c r="W10" t="n">
         <v>0.9786091279111153</v>
       </c>
-      <c r="X10" s="1" t="n">
+      <c r="X10" t="n">
         <v>0.4692280519442701</v>
       </c>
-      <c r="Y10" s="1" t="n">
+      <c r="Y10" t="n">
         <v>0.8909081386823086</v>
       </c>
-      <c r="Z10" s="1" t="n">
+      <c r="Z10" t="n">
         <v>0.8951653700752311</v>
       </c>
-      <c r="AA10" s="1" t="n">
+      <c r="AA10" t="n">
         <v>0.8909081386823086</v>
       </c>
-      <c r="AB10" s="1" t="n">
+      <c r="AB10" t="n">
         <v>0.8847231501252966</v>
       </c>
-      <c r="AC10" s="1" t="n">
+      <c r="AC10" t="n">
         <v>0.9715780125261124</v>
       </c>
-      <c r="AD10" s="1" t="n">
+      <c r="AD10" t="n">
         <v>0.2057901083028276</v>
       </c>
-      <c r="AE10" s="1" t="n">
+      <c r="AE10" t="n">
         <v>0.9424950246150623</v>
       </c>
-      <c r="AF10" s="1" t="n">
+      <c r="AF10" t="n">
         <v>0.9420985691162979</v>
       </c>
-      <c r="AG10" s="1" t="n">
+      <c r="AG10" t="n">
         <v>0.9424950246150623</v>
       </c>
-      <c r="AH10" s="1" t="n">
+      <c r="AH10" t="n">
         <v>0.9413223604999386</v>
       </c>
-      <c r="AI10" s="1" t="n">
+      <c r="AI10" t="n">
         <v>0.9922196362764649</v>
       </c>
-      <c r="AJ10" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK10" s="1" t="n">
+      <c r="AJ10" t="b">
+        <v>1</v>
+      </c>
+      <c r="AK10" t="n">
         <v>16</v>
       </c>
-      <c r="AL10" s="1" t="n">
+      <c r="AL10" t="n">
         <v>78.23285095400206</v>
       </c>
-      <c r="AM10" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="AN10" s="1" t="inlineStr">
+      <c r="AM10" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN10" t="inlineStr">
         <is>
           <t>NVIDIA GeForce RTX 5060</t>
         </is>
       </c>
-      <c r="AO10" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP10" s="1" t="n">
+      <c r="AO10" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP10" t="n">
         <v>92000</v>
       </c>
-      <c r="AQ10" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR10" s="1" t="b">
-        <v>0</v>
+      <c r="AQ10" t="b">
+        <v>1</v>
+      </c>
+      <c r="AR10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0.89</v>
       </c>
     </row>
     <row r="11">
@@ -2031,6 +2305,33 @@
       <c r="AR11" t="b">
         <v>0</v>
       </c>
+      <c r="AS11" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0.88</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2169,6 +2470,33 @@
       <c r="AR12" t="b">
         <v>0</v>
       </c>
+      <c r="AS12" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0.71</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2307,6 +2635,33 @@
       <c r="AR13" t="b">
         <v>0</v>
       </c>
+      <c r="AS13" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2445,6 +2800,33 @@
       <c r="AR14" t="b">
         <v>0</v>
       </c>
+      <c r="AS14" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0.7</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2583,6 +2965,33 @@
       <c r="AR15" t="b">
         <v>0</v>
       </c>
+      <c r="AS15" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0.83</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2721,6 +3130,33 @@
       <c r="AR16" t="b">
         <v>0</v>
       </c>
+      <c r="AS16" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0.86</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2859,6 +3295,33 @@
       <c r="AR17" t="b">
         <v>0</v>
       </c>
+      <c r="AS17" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0.88</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2997,6 +3460,33 @@
       <c r="AR18" t="b">
         <v>0</v>
       </c>
+      <c r="AS18" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0.88</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3135,6 +3625,33 @@
       <c r="AR19" t="b">
         <v>0</v>
       </c>
+      <c r="AS19" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0.85</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3273,6 +3790,33 @@
       <c r="AR20" t="b">
         <v>0</v>
       </c>
+      <c r="AS20" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>0.88</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3411,6 +3955,33 @@
       <c r="AR21" t="b">
         <v>0</v>
       </c>
+      <c r="AS21" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>0.89</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3549,6 +4120,33 @@
       <c r="AR22" t="b">
         <v>0</v>
       </c>
+      <c r="AS22" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>0.67</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3687,6 +4285,33 @@
       <c r="AR23" t="b">
         <v>0</v>
       </c>
+      <c r="AS23" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>0.67</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3825,6 +4450,33 @@
       <c r="AR24" t="b">
         <v>0</v>
       </c>
+      <c r="AS24" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>0.89</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3963,6 +4615,33 @@
       <c r="AR25" t="b">
         <v>0</v>
       </c>
+      <c r="AS25" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>0.76</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4101,6 +4780,33 @@
       <c r="AR26" t="b">
         <v>0</v>
       </c>
+      <c r="AS26" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>0.85</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4239,6 +4945,33 @@
       <c r="AR27" t="b">
         <v>0</v>
       </c>
+      <c r="AS27" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>0.85</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4377,143 +5110,197 @@
       <c r="AR28" t="b">
         <v>0</v>
       </c>
+      <c r="AS28" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>0.79</v>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="A29" t="inlineStr">
         <is>
           <t>2026-05-23_01-11-07</t>
         </is>
       </c>
-      <c r="B29" s="2" t="n">
+      <c r="B29" t="n">
         <v>100</v>
       </c>
-      <c r="C29" s="2" t="n">
+      <c r="C29" t="n">
         <v>42</v>
       </c>
-      <c r="D29" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E29" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F29" s="2" t="n">
+      <c r="D29" t="b">
+        <v>1</v>
+      </c>
+      <c r="E29" t="b">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
         <v>8</v>
       </c>
-      <c r="G29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I29" s="2" t="n">
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" t="n">
         <v>16</v>
       </c>
-      <c r="J29" s="2" t="n">
+      <c r="J29" t="n">
         <v>0.1398276356443244</v>
       </c>
-      <c r="K29" s="2" t="n">
+      <c r="K29" t="n">
         <v>32</v>
       </c>
-      <c r="L29" s="2" t="n">
+      <c r="L29" t="n">
         <v>5</v>
       </c>
-      <c r="M29" s="2" t="n">
+      <c r="M29" t="n">
         <v>0.0008679572756499553</v>
       </c>
-      <c r="N29" s="2" t="n">
+      <c r="N29" t="n">
         <v>47</v>
       </c>
-      <c r="O29" s="2" t="n">
+      <c r="O29" t="n">
         <v>6</v>
       </c>
-      <c r="P29" s="2" t="n">
+      <c r="P29" t="n">
         <v>9</v>
       </c>
-      <c r="Q29" s="2" t="n">
+      <c r="Q29" t="n">
         <v>0.4468604328327964</v>
       </c>
-      <c r="R29" s="2" t="n">
+      <c r="R29" t="n">
         <v>0.3142144190361623</v>
       </c>
-      <c r="S29" s="2" t="n">
+      <c r="S29" t="n">
         <v>0.8959790700546828</v>
       </c>
-      <c r="T29" s="2" t="n">
+      <c r="T29" t="n">
         <v>0.900980759799187</v>
       </c>
-      <c r="U29" s="2" t="n">
+      <c r="U29" t="n">
         <v>0.8959790700546828</v>
       </c>
-      <c r="V29" s="2" t="n">
+      <c r="V29" t="n">
         <v>0.8955904056853582</v>
       </c>
-      <c r="W29" s="2" t="n">
+      <c r="W29" t="n">
         <v>0.9808937791210707</v>
       </c>
-      <c r="X29" s="2" t="n">
+      <c r="X29" t="n">
         <v>0.4468604328327964</v>
       </c>
-      <c r="Y29" s="2" t="n">
+      <c r="Y29" t="n">
         <v>0.8949408191054782</v>
       </c>
-      <c r="Z29" s="2" t="n">
+      <c r="Z29" t="n">
         <v>0.8980189066981664</v>
       </c>
-      <c r="AA29" s="2" t="n">
+      <c r="AA29" t="n">
         <v>0.8949408191054782</v>
       </c>
-      <c r="AB29" s="2" t="n">
+      <c r="AB29" t="n">
         <v>0.8881435281136164</v>
       </c>
-      <c r="AC29" s="2" t="n">
+      <c r="AC29" t="n">
         <v>0.9719201064562083</v>
       </c>
-      <c r="AD29" s="2" t="n">
+      <c r="AD29" t="n">
         <v>0.1934452463814637</v>
       </c>
-      <c r="AE29" s="2" t="n">
+      <c r="AE29" t="n">
         <v>0.9400858908557662</v>
       </c>
-      <c r="AF29" s="2" t="n">
+      <c r="AF29" t="n">
         <v>0.9403057238519894</v>
       </c>
-      <c r="AG29" s="2" t="n">
+      <c r="AG29" t="n">
         <v>0.9400858908557662</v>
       </c>
-      <c r="AH29" s="2" t="n">
+      <c r="AH29" t="n">
         <v>0.9386899356682086</v>
       </c>
-      <c r="AI29" s="2" t="n">
+      <c r="AI29" t="n">
         <v>0.9920884963655692</v>
       </c>
-      <c r="AJ29" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK29" s="2" t="n">
+      <c r="AJ29" t="b">
+        <v>1</v>
+      </c>
+      <c r="AK29" t="n">
         <v>17</v>
       </c>
-      <c r="AL29" s="2" t="n">
+      <c r="AL29" t="n">
         <v>291.0554734269972</v>
       </c>
-      <c r="AM29" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="AN29" s="2" t="inlineStr">
+      <c r="AM29" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN29" t="inlineStr">
         <is>
           <t>NVIDIA GeForce RTX 5060</t>
         </is>
       </c>
-      <c r="AO29" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP29" s="2" t="n">
+      <c r="AO29" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP29" t="n">
         <v>92000</v>
       </c>
-      <c r="AQ29" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR29" s="2" t="b">
-        <v>0</v>
+      <c r="AQ29" t="b">
+        <v>1</v>
+      </c>
+      <c r="AR29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>0.89</v>
       </c>
     </row>
     <row r="30">
@@ -4653,6 +5440,33 @@
       <c r="AR30" t="b">
         <v>0</v>
       </c>
+      <c r="AS30" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4790,6 +5604,33 @@
       </c>
       <c r="AR31" t="b">
         <v>0</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>0.87</v>
       </c>
     </row>
   </sheetData>
